--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20261005.xlsx
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>12月までに印刷の発注をしないと2月の校了に間に合わない</t>
+          <t>年度末は印刷が集中するため、1月中に印刷業者を押さえる</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20261005.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>準備基金の保有額12,000千円と繰越金144.2百万円の不整合の確認</t>
+          <t>準備基金の令和7年度末の残高と令和8年度9月補正の積立の確認（令和8年度末見込210,000千円）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>年報 様式4 の基金保有額は12,000千円ですが、令和4年度末の120,000千円から1桁減っています。一方で歳入歳出差引残額は令和6年度末で144,205,672円あり、繰越金として滞留しています。基金運用状況調書で実額をご確認ください。取崩実績なのか年報の入力誤りなのかで、打てる手が変わります</t>
+          <t>基金の残高は、町の財務書類で令和5年度末120,000千円、令和8年度末見込210,000千円です。一方で歳入歳出差引残額は令和6年度末で144,205,672円あり、繰越金として滞留しています。令和7年度末の残高（財産に関する調書）と令和8年度9月補正の積立の執行をご確認ください。第10期にどれだけ取り崩すかで、打てる手が変わります</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr"/>
@@ -1702,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1784,24 +1784,24 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>当方の算定　基金12,000千円を全額取崩</t>
+          <t>当方の算定　基金105,000千円を取崩</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>5949.52</v>
+        <v>5188.08</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>6000</v>
+        <v>5200</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>72000</v>
+        <v>62400</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>-600</v>
+        <v>-1400</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>年報 様式4 の保有額をすべて投入した場合</t>
+          <t>令和8年度末見込210,000千円の半分を充てた場合</t>
         </is>
       </c>
     </row>
@@ -1830,90 +1830,90 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>基金が12,000千円しかなければ実行できない</t>
+          <t>残高の範囲内で実行できる</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>当方の算定　基金210,000千円を全額取崩</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>4328.4</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>4400</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>52800</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>-2200</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>令和8年度末見込の全額を充てた場合。第10期末の残高は0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>B-1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>見える化システム　取崩なし</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C6" s="8" t="n">
         <v>6533.46</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D6" s="9" t="n">
         <v>6600</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E6" s="8" t="n">
         <v>79200</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>対案。令和8年度を月報の1か月で置く。第9期と同額の据え置きになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>B-2</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>見える化システム　基金12,000千円を全額取崩</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>6435.16</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>78000</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>―</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>B-3</t>
+          <t>B-2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>見える化システム　35,000千円を取崩</t>
+          <t>見える化システム　基金105,000千円を取崩</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>6246.76</v>
+        <v>5673.36</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>6300</v>
+        <v>5700</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>75600</v>
+        <v>68400</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>-300</v>
+        <v>-900</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -1924,513 +1924,594 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>B-3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>当方の算定　第1号被保険者負担割合24％</t>
+          <t>見える化システム　35,000千円を取崩</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>6316.79</v>
+        <v>6246.76</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>76800</v>
+        <v>75600</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>国の第10期の負担割合は未定。23％から上がれば保険料も上がる</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>B-4</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>見える化システム　基金210,000千円を全額取崩</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>4813.26</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>4900</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>58800</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>-1700</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>当方の算定　第1号被保険者負担割合24％</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>6316.79</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>76800</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>国の第10期の負担割合は未定。23％から上がれば保険料も上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>C-2</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>システム　第1号被保険者負担割合24％</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C11" s="8" t="n">
         <v>6823.95</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D11" s="8" t="n">
         <v>6900</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E11" s="8" t="n">
         <v>82800</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F11" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>【所得段階別の年額（円）】</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>乗率（賦課割合）</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>A-1（基準73,200円）</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>B-1（基準79,200円）</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>第9期（79,200円）</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>被保険者数（人）</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>第1段階</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>20900</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>22600</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>22600</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>525</v>
-      </c>
-      <c r="G13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>第2段階</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>35600</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>38500</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>38500</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>297</v>
-      </c>
-      <c r="G14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>第3段階</t>
+          <t>第1段階</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.285</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>50200</v>
+        <v>20900</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>54300</v>
+        <v>22600</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>54300</v>
+        <v>22600</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>272</v>
+        <v>525</v>
       </c>
       <c r="G15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>第4段階</t>
+          <t>第2段階</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>0.9</v>
+        <v>0.485</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>65900</v>
+        <v>35600</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>71300</v>
+        <v>38500</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>71300</v>
+        <v>38500</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>434</v>
+        <v>297</v>
       </c>
       <c r="G16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>第5段階</t>
+          <t>第3段階</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>1</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>73200</v>
+        <v>50200</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>79200</v>
+        <v>54300</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>79200</v>
+        <v>54300</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>610</v>
+        <v>272</v>
       </c>
       <c r="G17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>第6段階</t>
+          <t>第4段階</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>87900</v>
+        <v>65900</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>95100</v>
+        <v>71300</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>95100</v>
+        <v>71300</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>491</v>
+        <v>434</v>
       </c>
       <c r="G18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>第7段階</t>
+          <t>第5段階</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>95200</v>
+        <v>73200</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>103000</v>
+        <v>79200</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>103000</v>
+        <v>79200</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>418</v>
+        <v>610</v>
       </c>
       <c r="G19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>第8段階</t>
+          <t>第6段階</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>109800</v>
+        <v>87900</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>118800</v>
+        <v>95100</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>118800</v>
+        <v>95100</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>231</v>
+        <v>491</v>
       </c>
       <c r="G20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>第9段階</t>
+          <t>第7段階</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>124500</v>
+        <v>95200</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>134700</v>
+        <v>103000</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>134700</v>
+        <v>103000</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>77</v>
+        <v>418</v>
       </c>
       <c r="G21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>第10段階</t>
+          <t>第8段階</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>139100</v>
+        <v>109800</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>150500</v>
+        <v>118800</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>150500</v>
+        <v>118800</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>36</v>
+        <v>231</v>
       </c>
       <c r="G22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>第11段階</t>
+          <t>第9段階</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>153800</v>
+        <v>124500</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>166400</v>
+        <v>134700</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>166400</v>
+        <v>134700</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>第12段階</t>
+          <t>第10段階</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>168400</v>
+        <v>139100</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>182200</v>
+        <v>150500</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>182200</v>
+        <v>150500</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>第13段階</t>
+          <t>第11段階</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>175700</v>
+        <v>153800</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>190100</v>
+        <v>166400</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>190100</v>
+        <v>166400</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>第12段階</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>168400</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>182200</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>182200</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>第13段階</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>175700</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>190100</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>190100</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n">
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n">
         <v>3443</v>
       </c>
-      <c r="G26" s="2" t="n"/>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>【準備基金】</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>額</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>出所</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>介護給付費準備基金 保有額（令和7年度末）</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>年報 様式4</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>令和4年度末の120,000千円から1桁減っている</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>歳入歳出差引残額（令和6年度末）</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>144205672</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>年報 様式4</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>繰越金として滞留している</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>第9期の取崩額</t>
+          <t>介護給付費準備基金 残高（令和5年度末）</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>35000000</v>
+        <v>120000000</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>第9期計画</t>
+          <t>町の財務書類</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>基金が12,000千円しかなければ同額の取崩はできない</t>
+          <t>財産に関する調書の記載額と同じ</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>同（令和8年度末見込）</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>決算・令和8年度予算</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>以後の積立と令和8年度予算（当初・9月補正）の積立</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>歳入歳出差引残額（令和6年度末）</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>144205672</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>年報 様式4</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>繰越金として滞留している</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>第9期の取崩額</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>第9期計画</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>残高の範囲内で実行できる</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/19_打合せ/小野町_打合せ_決定依頼事項一覧_20261005.xlsx
@@ -2879,7 +2879,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>第8版。第7版（9月29日）で、お預かりした調査結果報告書の原本（104頁）と集計値を1件ずつ突き合わせ、認知症の設問の項目名（54.1％）を訂正した。第8版では、他団体の第10期計画との構成の対比で残っていた3項目を埋めた。①第6章10「中長期の見通し（令和22年・令和32年）」を新設（総給付費は令和22年で＋12.8％にとどまるが、第1号被保険者1人当たりでは＋28.7％、令和32年では＋39.5％になる）。②第1章2に、国が第10期に求める5点と確認すべき制度改正5件の表を加えた。③資料編12「図表番号一覧」を新設し、すべての表に通し番号を振った</t>
+          <t>第8版。第7版（9月29日）で、お預かりした調査結果報告書の原本（104頁）と集計値を1件ずつ突き合わせ、認知症の設問の項目名（54.1％）を原本に合わせた。第8版では、他団体の第10期計画との構成の対比で残っていた3項目を埋めた。①第6章10「中長期の見通し（令和22年・令和32年）」を新設（総給付費は令和22年で＋12.8％にとどまるが、第1号被保険者1人当たりでは＋28.7％、令和32年では＋39.5％になる）。②第1章2に、国が第10期に求める5点と確認すべき制度改正5件の表を加えた。③資料編12「図表番号一覧」を新設し、すべての表に通し番号を振った</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>協議会第1回の資料（第2版）。年報により第9期の実績を確定させ、次回お諮りする保険料2案を明記した。第3版。9月29日に、調査結果報告書の原本との突合により認知症の設問の項目名を訂正し、報告書の食い違い3件を第2部に注記した。開催日が決まり次第お出しできます</t>
+          <t>協議会第1回の資料（第2版）。年報により第9期の実績を確定させ、次回お諮りする保険料2案を明記した。第3版。9月29日に、調査結果報告書の原本と突き合わせ、認知症の設問の項目名を原本に合わせ、報告書の食い違い3件を第2部に注記した。開催日が決まり次第お出しできます</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>9月29日に、お預かりした調査結果報告書の原本（104頁）と集計値を1件ずつ突き合わせ、認知症の設問の項目名を訂正した。報告書そのものの中の食い違い2件（回収数と集計の基数、通いの場の本文と図）は第4章に記載</t>
+          <t>9月29日に、お預かりした調査結果報告書の原本（104頁）と集計値を1件ずつ突き合わせ、認知症の設問の項目名を原本に合わせた。報告書そのものの中の食い違い2件（回収数と集計の基数、通いの場の本文と図）は第4章に記載</t>
         </is>
       </c>
     </row>
